--- a/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
@@ -473,7 +473,7 @@
     <row r="3" ht="19" customHeight="1" s="12">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>기준일: 2026-10-23 · 총 16편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
+          <t>기준일: 2026-10-23 · 총 15편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -1236,54 +1236,16 @@
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" s="12">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>N26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Bolzenkötter, Neubauer &amp; Koval</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Impact of a Momentary Mindfulness Intervention on Rumination, Negative Affect, and their Dynamics in Daily Life</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s42761-024-00291-9</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12209136/</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>PMC 오픈 액세스 전문 있음</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>"Impact of a Momentary Mindfulness Intervention on Rumination" PDF</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>36편 근거 목록 N01 · 공개본 바로 내려받기 가능</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="6" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1" s="12">
       <c r="A22" s="7" t="n"/>

--- a/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
@@ -473,7 +473,7 @@
     <row r="3" ht="19" customHeight="1" s="12">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>기준일: 2026-10-23 · 총 15편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
+          <t>기준일: 2026-10-23 · 총 12편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -1086,154 +1086,40 @@
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" s="12">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>P37</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Laumann, Gärling &amp; Stormark</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2003</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Selective attention and heart rate responses to natural and urban environments</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/S0272-4944(02)00110-X</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/S0272-4944(02)00110-X</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>출판사/기관 구독 필요</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>"Selective attention and heart rate responses to natural and urban environments" PDF</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>36편 근거 목록 P06</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="6" t="n"/>
     </row>
     <row r="19" ht="48" customHeight="1" s="12">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>P38</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Lymeus, Lindberg &amp; Hartig</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Building mindfulness bottom-up: Meditation in natural settings supports open monitoring and attention restoration</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.concog.2018.01.008</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.concog.2018.01.008</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>출판사 구독·공개 전문 미확인</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>"Building mindfulness bottom-up" Lymeus PDF</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>36편 근거 목록 P12</t>
-        </is>
-      </c>
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1" s="12">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>P39</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Lymeus, Lindberg &amp; Hartig</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>A natural meditation setting improves compliance with mindfulness training</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.jenvp.2019.05.008</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jenvp.2019.05.008</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>출판사 구독·공개 전문 미확인</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>"A natural meditation setting improves compliance with mindfulness training" PDF</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>36편 근거 목록 P13</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1" s="12">
       <c r="A21" s="3" t="n"/>

--- a/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J22"/>
+  <dimension ref="A2:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="12" min="1" max="1"/>
@@ -473,7 +473,7 @@
     <row r="3" ht="19" customHeight="1" s="12">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>기준일: 2026-10-23 · 총 12편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
+          <t>기준일: 2026-10-23 · 총 6편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -624,43 +624,43 @@
     <row r="8" ht="48" customHeight="1" s="12">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>N06</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>저자 확인 필요</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Ground yourself: Using five senses technique to cope with test anxiety among nursing students</t>
+          <t>Development and Validation of an Internationally Reliable Short-Form of the Positive and Negative Affect Schedule (PANAS)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.teln.2025.09.022</t>
+          <t>10.1177/0022022106297301</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.teln.2025.09.022</t>
+          <t>https://doi.org/10.1177/0022022106297301</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>신규 출판 논문·출판사 원문 제한</t>
+          <t>SAGE/기관 구독 필요</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>"Ground yourself" "five senses technique" PDF</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
+          <t>"Internationally Reliable Short-Form" PANAS Thompson PDF</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>미확보</t>
         </is>
@@ -670,40 +670,40 @@
     <row r="9" ht="48" customHeight="1" s="12">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>N06</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Hartig, Korpela, Evans &amp; Gärling</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Development and Validation of an Internationally Reliable Short-Form of the Positive and Negative Affect Schedule (PANAS)</t>
+          <t>A measure of restorative quality in environments</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10.1177/0022022106297301</t>
+          <t>10.1080/02815739708730435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0022022106297301</t>
+          <t>https://doi.org/10.1080/02815739708730435</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>SAGE/기관 구독 필요</t>
+          <t>출판사/ResearchGate 원문 제한</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>"Internationally Reliable Short-Form" PANAS Thompson PDF</t>
+          <t>"A measure of restorative quality in environments" PDF</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -716,43 +716,43 @@
     <row r="10" ht="48" customHeight="1" s="12">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Hartig, Korpela, Evans &amp; Gärling</t>
+          <t>Axelsson, Nilsson &amp; Berglund</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1997</v>
+        <v>2010</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>A measure of restorative quality in environments</t>
+          <t>A principal components model of soundscape perception</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10.1080/02815739708730435</t>
+          <t>10.1121/1.3493436</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02815739708730435</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21110579/</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>출판사/ResearchGate 원문 제한</t>
+          <t>저자 업로드본이 있으나 로그인/캡차 차단</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>"A measure of restorative quality in environments" PDF</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
+          <t>"A principal components model of soundscape perception" PDF</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>미확보</t>
         </is>
@@ -762,40 +762,40 @@
     <row r="11" ht="48" customHeight="1" s="12">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Laumann, Gärling &amp; Stormark</t>
+          <t>Flicker et al.</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2001</v>
+        <v>2025</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Rating Scale Measures of Restorative Components of Environments</t>
+          <t>Mechanisms of Anxiety Reduction During Adult Coloring: Mindfulness, Flow, Enjoyment, and Distraction</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10.1006/jevp.2000.0179</t>
+          <t>10.1007/s12671-025-02586-9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1006/jevp.2000.0179</t>
+          <t>https://doi.org/10.1007/s12671-025-02586-9</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>MUNI 공개본이 브라우저 보안 확인으로 차단</t>
+          <t>구독 논문·대학 저장소는 서지정보만</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>"Rating Scale Measures of Restorative Components of Environments" PDF</t>
+          <t>"Mechanisms of Anxiety Reduction During Adult Coloring" PDF</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -803,348 +803,78 @@
           <t>미확보</t>
         </is>
       </c>
-      <c r="J11" s="6" t="str"/>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>36편 근거 목록 P30</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>N13</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Grahn &amp; Stigsdotter</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>2010</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>The relation between perceived sensory dimensions of urban green space and stress restoration</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.landurbplan.2009.10.012</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.landurbplan.2009.10.012</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>기존 SLU 공개 링크 만료</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>"perceived sensory dimensions of urban green space" PDF</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="str"/>
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="6" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1" s="12">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>N19</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Hicks et al.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Restoration of sustained attention following virtual nature exposure: Undeniable or unreliable?</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.jenvp.2020.101488</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0272494420304655</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>동일 제목 학위논문만 공개·저널본 제한</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>"Restoration of sustained attention following virtual nature exposure" PDF</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="str"/>
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1" s="12">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>N22</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Joye &amp; van den Berg</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Is love for green in our genes? A critical analysis of evolutionary assumptions in restorative environments research</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.ufug.2011.07.004</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ufug.2011.07.004</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>저자 공개 링크가 현재 다른 페이지로 이동</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>"Is love for green in our genes" PDF</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="str"/>
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="6" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1" s="12">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>N23</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Axelsson, Nilsson &amp; Berglund</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>2010</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>A principal components model of soundscape perception</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>10.1121/1.3493436</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/21110579/</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>저자 업로드본이 있으나 로그인/캡차 차단</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>"A principal components model of soundscape perception" PDF</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="str"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="6" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1" s="12">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>N25</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Chiorri et al.</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Measurement Invariance of the Brief State Rumination Inventory Across Administration Methods, National Samples, and Sex</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10.1080/00223891.2026.2726459</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tandfonline.com/doi/full/10.1080/00223891.2026.2726459</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>UGent 수락원고 엠바고: 2027-08-19 공개 예정</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>"Measurement Invariance of the Brief State Rumination Inventory" PDF</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="str"/>
-    </row>
-    <row r="17" ht="48" customHeight="1" s="12">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>P30</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Flicker et al.</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Mechanisms of Anxiety Reduction During Adult Coloring: Mindfulness, Flow, Enjoyment, and Distraction</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s12671-025-02586-9</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s12671-025-02586-9</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>구독 논문·대학 저장소는 서지정보만</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>"Mechanisms of Anxiety Reduction During Adult Coloring" PDF</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>미확보</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>36편 근거 목록 P30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1" s="12">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="48" customHeight="1" s="12">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="48" customHeight="1" s="12">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1" s="12">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="48" customHeight="1" s="12">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="10" t="n"/>
-    </row>
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="12"/>
+    <row r="18" ht="48" customHeight="1" s="12"/>
+    <row r="19" ht="48" customHeight="1" s="12"/>
+    <row r="20" ht="48" customHeight="1" s="12"/>
+    <row r="21" ht="48" customHeight="1" s="12"/>
+    <row r="22" ht="48" customHeight="1" s="12"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:J3"/>

--- a/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/미확보_논문_직접검색_목록_2026-10-22.xlsx
@@ -473,7 +473,7 @@
     <row r="3" ht="19" customHeight="1" s="12">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>기준일: 2026-10-23 · 총 6편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
+          <t>기준일: 2026-10-29 · 총 7편 · DOI와 검색 문구를 이용해 합법적 공개본 또는 기관 구독본을 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -810,16 +810,54 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="6" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>N28</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Marchetti, Mor, Chiorri &amp; Koster</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>The Brief State Rumination Inventory (BSRI): Validation and Psychometric Evaluation</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10608-018-9901-1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10608-018-9901-1</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Springer 구독 필요 — 저자 척도 소개 문서(문항·채점·사용 조건)는 확보</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>"The Brief State Rumination Inventory (BSRI): Validation and Psychometric Evaluation" PDF</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>미확보</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>저자 척도 소개 문서: 00_original_PDF/N28_2018_Marchetti_BSRI_author_overview_items_and_scoring.pdf (2018 논문 원문 아님)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="48" customHeight="1" s="12">
       <c r="A13" s="3" t="n"/>
